--- a/src/attributions/attributions_saliency_traj_499.xlsx
+++ b/src/attributions/attributions_saliency_traj_499.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.001754606491886079</v>
+        <v>0.126196026802063</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001777959405444562</v>
+        <v>0.4740498065948486</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001120834378525615</v>
+        <v>0.1788223087787628</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004016589373350143</v>
+        <v>0.1696376204490662</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008744585793465376</v>
+        <v>0.2365318089723587</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002035632642218843</v>
+        <v>0.2591834664344788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001417377614416182</v>
+        <v>0.01820502802729607</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003286282881163061</v>
+        <v>0.06180914491415024</v>
       </c>
       <c r="I2" t="n">
-        <v>6.886640039738268e-05</v>
+        <v>0.1525525897741318</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002073989948257804</v>
+        <v>0.1533470153808594</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001416653976775706</v>
+        <v>0.4787760376930237</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007442363421432674</v>
+        <v>0.1498599946498871</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004606277216225863</v>
+        <v>0.07369722425937653</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007190199103206396</v>
+        <v>0.4048517346382141</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002032072050496936</v>
+        <v>0.04431385546922684</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000147491751704365</v>
+        <v>0.02379174530506134</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001229967689141631</v>
+        <v>0.05702996253967285</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009951511165127158</v>
+        <v>0.02758919633924961</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000429465901106596</v>
+        <v>0.02713514678180218</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008939016843214631</v>
+        <v>0.01121740788221359</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006867075571790338</v>
+        <v>0.01812595687806606</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0004038789193145931</v>
+        <v>0.1181819289922714</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001617243397049606</v>
+        <v>0.03588636964559555</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00101487641222775</v>
+        <v>0.2415750771760941</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0005453828489407897</v>
+        <v>0.03310425952076912</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001321452204138041</v>
+        <v>0.0275118313729763</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.36046253121458e-05</v>
+        <v>0.2041236013174057</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0006420247373171151</v>
+        <v>0.1104931756854057</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.001132911304011941</v>
+        <v>0.05668090283870697</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0008127611363306642</v>
+        <v>0.05319815129041672</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0004678583063650876</v>
+        <v>0.09708830714225769</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0008771519642323256</v>
+        <v>0.09952975809574127</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0009533445117995143</v>
+        <v>0.03444978967308998</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0005029041785746813</v>
+        <v>0.0468023382127285</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.003598173265345e-05</v>
+        <v>0.00815022736787796</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0006728211883455515</v>
+        <v>0.05962059646844864</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.00041783886263147</v>
+        <v>0.03057598322629929</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.001761141582392156</v>
+        <v>0.1523268222808838</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0003719684609677643</v>
+        <v>0.02120990492403507</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0008952082716859877</v>
+        <v>0.05072711780667305</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0003177184844389558</v>
+        <v>0.3472925424575806</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0005896556540392339</v>
+        <v>0.04961976408958435</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0001200065162265673</v>
+        <v>0.004544970579445362</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.00035045703407377</v>
+        <v>0.05936950072646141</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0009188601397909224</v>
+        <v>0.1238217130303383</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0006259909132495522</v>
+        <v>0.04792273044586182</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.001187238725833595</v>
+        <v>0.29416224360466</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0005939698312431574</v>
+        <v>0.04476843774318695</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0006781402626074851</v>
+        <v>0.02459784783422947</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0001735024125082418</v>
+        <v>0.0593334324657917</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.001002419972792268</v>
+        <v>0.0490984171628952</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0001573318731971085</v>
+        <v>0.008409859612584114</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0001059078495018184</v>
+        <v>0.0172641072422266</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0003473657998256385</v>
+        <v>0.08263562619686127</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0003733294433914125</v>
+        <v>0.09228665381669998</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0003456552512943745</v>
+        <v>0.1128882244229317</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0002767109544947743</v>
+        <v>0.2437407374382019</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.001764470944181085</v>
+        <v>0.1235688179731369</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0005129294586367905</v>
+        <v>0.302132248878479</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0001839228498283774</v>
+        <v>0.2214421927928925</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0007951530278660357</v>
+        <v>0.1046396270394325</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.000358313147444278</v>
+        <v>0.04902758449316025</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.001116806059144437</v>
+        <v>0.01963656581938267</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.001930131809785962</v>
+        <v>0.02560941688716412</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.001150695024989545</v>
+        <v>0.1387103199958801</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.787976361811161e-05</v>
+        <v>0.0007981695234775543</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0003838514385279268</v>
+        <v>0.2500677406787872</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.000222015893086791</v>
+        <v>0.03083261474967003</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.000619741331320256</v>
+        <v>0.03551210835576057</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0003246865817345679</v>
+        <v>0.05314727872610092</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0003255271585658193</v>
+        <v>0.006573472172021866</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0002076693635899574</v>
+        <v>0.1365917772054672</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0007859764155000448</v>
+        <v>0.05689726769924164</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0006162981153465807</v>
+        <v>0.2430607527494431</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.000633406569249928</v>
+        <v>0.04990388453006744</v>
       </c>
       <c r="BX2" t="n">
-        <v>7.246059976750985e-05</v>
+        <v>0.1554417014122009</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.001380055211484432</v>
+        <v>0.002336064353585243</v>
       </c>
       <c r="BZ2" t="n">
-        <v>6.326096627162769e-05</v>
+        <v>0.1060913354158401</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0002922783023677766</v>
+        <v>0.01911427080631256</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.0003588296822272241</v>
+        <v>0.06071433797478676</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.0004726642509922385</v>
+        <v>0.1980155110359192</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.001174705103039742</v>
+        <v>0.04410319030284882</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0002622714673634619</v>
+        <v>0.1712186932563782</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0001887840771814808</v>
+        <v>0.08349613845348358</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0009994104038923979</v>
+        <v>0.03201838210225105</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0002302034408785403</v>
+        <v>0.0315619558095932</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0003668310819193721</v>
+        <v>0.01238557230681181</v>
       </c>
       <c r="CJ2" t="n">
-        <v>9.96698800008744e-05</v>
+        <v>0.01092834677547216</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0001991850294871256</v>
+        <v>0.03306860476732254</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0001050188730005175</v>
+        <v>0.02613752707839012</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.0003022708697244525</v>
+        <v>0.09970661997795105</v>
       </c>
       <c r="CN2" t="n">
-        <v>8.520515984855592e-05</v>
+        <v>0.09148912131786346</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0002107712207362056</v>
+        <v>0.2075474113225937</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0001199797552544624</v>
+        <v>0.1351559609174728</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.000919884187169373</v>
+        <v>0.04367741942405701</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0002438901283312589</v>
+        <v>0.02527037635445595</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0008630980737507343</v>
+        <v>0.07767812162637711</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.0005573917296715081</v>
+        <v>0.004534547217190266</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.00130100769456476</v>
+        <v>0.1140254735946655</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.001203915802761912</v>
+        <v>0.02778017520904541</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0001417133753420785</v>
+        <v>0.1660089492797852</v>
       </c>
       <c r="CX2" t="n">
-        <v>9.514174598734826e-05</v>
+        <v>0.05743693187832832</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0007860083132982254</v>
+        <v>0.0217102412134409</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.132550071110018e-05</v>
+        <v>0.002365450374782085</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0004990854067727923</v>
+        <v>0.02140412479639053</v>
       </c>
       <c r="DB2" t="n">
-        <v>7.565418491140008e-05</v>
+        <v>0.03702486306428909</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0002855685888789594</v>
+        <v>0.02156692743301392</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.387480642733863e-05</v>
+        <v>0.04687651246786118</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.0001204506115755066</v>
+        <v>0.05322534218430519</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.001313401036895812</v>
+        <v>0.1287661492824554</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0007641489501111209</v>
+        <v>0.05639076977968216</v>
       </c>
       <c r="DH2" t="n">
-        <v>9.271075396100059e-05</v>
+        <v>0.03181781619787216</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0002256590960314497</v>
+        <v>0.06198537349700928</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0002752221480477601</v>
+        <v>0.01863498985767365</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.001907362486235797</v>
+        <v>0.03199857845902443</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.194480864796788e-05</v>
+        <v>0.03552459925413132</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.001914367661811411</v>
+        <v>0.08056143671274185</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.000683351478073746</v>
+        <v>0.04182255268096924</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0004864971269853413</v>
+        <v>0.06246062368154526</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.001112466095946729</v>
+        <v>0.1053052991628647</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.001265911851078272</v>
+        <v>0.0674484521150589</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.001216406933963299</v>
+        <v>0.1331440806388855</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0007214384968392551</v>
+        <v>0.1351360678672791</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0005101384012959898</v>
+        <v>0.03330623731017113</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0001702255103737116</v>
+        <v>0.05916601419448853</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0007457251776941121</v>
+        <v>0.0743788480758667</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.001192152965813875</v>
+        <v>0.1069355979561806</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.001326717901974916</v>
+        <v>0.008447242900729179</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0009123856434598565</v>
+        <v>0.1210401505231857</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.001124119269661605</v>
+        <v>0.01724722236394882</v>
       </c>
       <c r="EA2" t="n">
-        <v>4.607994924299419e-05</v>
+        <v>0.1931523531675339</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.001005593920126557</v>
+        <v>0.09270062297582626</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.000283252855297178</v>
+        <v>0.02784506045281887</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0009491195087321103</v>
+        <v>0.009146165102720261</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0007719402783550322</v>
+        <v>0.04682224243879318</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0003655496693681926</v>
+        <v>0.01568689197301865</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0001508185087004676</v>
+        <v>0.1404616087675095</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0001046046818373725</v>
+        <v>0.01568189263343811</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.002480720169842243</v>
+        <v>0.1732029914855957</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0002462422417011112</v>
+        <v>0.07748698443174362</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0002834755287040025</v>
+        <v>0.02246526628732681</v>
       </c>
       <c r="EL2" t="n">
-        <v>3.888938226737082e-05</v>
+        <v>0.0162352416664362</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.000944889266975224</v>
+        <v>0.01765736006200314</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.00043240882223472</v>
+        <v>0.01920714415609837</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.001323794946074486</v>
+        <v>0.05201681703329086</v>
       </c>
       <c r="EP2" t="n">
-        <v>6.786978337913752e-05</v>
+        <v>0.1571397185325623</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.0007716879481449723</v>
+        <v>0.04751592129468918</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0004665349260903895</v>
+        <v>0.003913905471563339</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0001469024282414466</v>
+        <v>0.03774739801883698</v>
       </c>
       <c r="ET2" t="n">
-        <v>4.193518179818057e-05</v>
+        <v>0.09457983076572418</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.0002885486173909158</v>
+        <v>0.01886958442628384</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.001503924140706658</v>
+        <v>0.08900007605552673</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.0004500369832385331</v>
+        <v>0.06733812391757965</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.001316034467890859</v>
+        <v>0.06236547976732254</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.0002261569607071579</v>
+        <v>0.1933613121509552</v>
       </c>
       <c r="EZ2" t="n">
-        <v>6.943259359104559e-05</v>
+        <v>0.07011479884386063</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.001024012337438762</v>
+        <v>0.01406063884496689</v>
       </c>
       <c r="FB2" t="n">
-        <v>7.581402314826846e-05</v>
+        <v>0.01613112166523933</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0001964737894013524</v>
+        <v>0.0282167736440897</v>
       </c>
       <c r="FD2" t="n">
-        <v>3.541555997799151e-05</v>
+        <v>0.01893566362559795</v>
       </c>
       <c r="FE2" t="n">
-        <v>8.554661326343194e-05</v>
+        <v>0.06259835511445999</v>
       </c>
       <c r="FF2" t="n">
-        <v>5.064260403742082e-05</v>
+        <v>0.0512920469045639</v>
       </c>
       <c r="FG2" t="n">
-        <v>1.296796835958958e-05</v>
+        <v>0.01864437200129032</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.001463005552068353</v>
+        <v>0.1585410982370377</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0002945977030321956</v>
+        <v>0.1298483461141586</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0006744017591699958</v>
+        <v>0.04825180768966675</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.00135689543094486</v>
+        <v>0.06841522455215454</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0008936421945691109</v>
+        <v>0.09439658373594284</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0004771417588926852</v>
+        <v>0.02051509916782379</v>
       </c>
       <c r="FN2" t="n">
-        <v>4.642961357603781e-05</v>
+        <v>0.1342401206493378</v>
       </c>
       <c r="FO2" t="n">
-        <v>6.260833470150828e-05</v>
+        <v>0.2175038009881973</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.002268152544274926</v>
+        <v>0.04384978860616684</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0004994447808712721</v>
+        <v>0.1928013563156128</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.0002374115429120138</v>
+        <v>0.2906756997108459</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0003556277661118656</v>
+        <v>0.3047254979610443</v>
       </c>
       <c r="FT2" t="n">
-        <v>7.413119601551443e-05</v>
+        <v>0.1102189421653748</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0009620258933864534</v>
+        <v>0.2524427771568298</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.003669213736429811</v>
+        <v>0.01961204782128334</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.002440489362925291</v>
+        <v>0.1014585942029953</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0002953282673843205</v>
+        <v>0.1462298035621643</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.001762636820785701</v>
+        <v>0.07944604009389877</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.000279879430308938</v>
+        <v>0.130203902721405</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.001507606822997332</v>
+        <v>0.02826038748025894</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0007500199717469513</v>
+        <v>0.05164411664009094</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0005088732577860355</v>
+        <v>0.01495590806007385</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.001615565735846758</v>
+        <v>0.003980387002229691</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.001981242327019572</v>
+        <v>0.05831378698348999</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.001520392019301653</v>
+        <v>0.1807070076465607</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.001355156069621444</v>
+        <v>0.1579686999320984</v>
       </c>
     </row>
     <row r="3">
